--- a/Dataset_2/4_Integration_results/Stats_table_final.xlsx
+++ b/Dataset_2/4_Integration_results/Stats_table_final.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
   <si>
     <t xml:space="preserve">metric</t>
   </si>
@@ -47,13 +47,25 @@
     <t xml:space="preserve">Recall genes</t>
   </si>
   <si>
-    <t xml:space="preserve">Tot.associations...intersection</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Perc.sig.Spearman</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Perc.unique.sig.Spearman</t>
+    <t xml:space="preserve">Tot associations - intersection</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Perc sig CpG-gene Delta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Perc sig genes Delta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Perc unique sig Delta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Perc sig CpG-gene eQTM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Perc sig genes eQTM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Perc unique sig eQTM</t>
   </si>
   <si>
     <t xml:space="preserve">expected_perc</t>
@@ -62,6 +74,9 @@
     <t xml:space="preserve">odds_ratio</t>
   </si>
   <si>
+    <t xml:space="preserve">pvalue_quadrants</t>
+  </si>
+  <si>
     <t xml:space="preserve">pvalue_quadrants_BH</t>
   </si>
   <si>
@@ -74,7 +89,7 @@
     <t xml:space="preserve">DM ∩ DE DM up (padj)</t>
   </si>
   <si>
-    <t xml:space="preserve">M ∩ DE vs All DM up (padj)</t>
+    <t xml:space="preserve">DM ∩ DE vs All DM up (padj)</t>
   </si>
   <si>
     <t xml:space="preserve">All DM down (padj)</t>
@@ -83,7 +98,7 @@
     <t xml:space="preserve">DM ∩ DE DM down (padj)</t>
   </si>
   <si>
-    <t xml:space="preserve">M ∩ DE vs All DM down (padj)</t>
+    <t xml:space="preserve">DM ∩ DE vs All DM down (padj)</t>
   </si>
   <si>
     <t xml:space="preserve">Hypo-up (padj)</t>
@@ -473,19 +488,19 @@
         <v>6</v>
       </c>
       <c r="B2" t="n">
-        <v>22463</v>
+        <v>25296</v>
       </c>
       <c r="C2" t="n">
-        <v>28328</v>
+        <v>32549</v>
       </c>
       <c r="D2" t="n">
-        <v>12643</v>
+        <v>22829</v>
       </c>
       <c r="E2" t="n">
-        <v>27175</v>
+        <v>32901</v>
       </c>
       <c r="F2" t="n">
-        <v>30319</v>
+        <v>32886</v>
       </c>
     </row>
     <row r="3">
@@ -493,19 +508,19 @@
         <v>7</v>
       </c>
       <c r="B3" t="n">
-        <v>5817</v>
+        <v>6195</v>
       </c>
       <c r="C3" t="n">
-        <v>5934</v>
+        <v>6377</v>
       </c>
       <c r="D3" t="n">
-        <v>3412</v>
+        <v>5248</v>
       </c>
       <c r="E3" t="n">
-        <v>5417</v>
+        <v>6191</v>
       </c>
       <c r="F3" t="n">
-        <v>5868</v>
+        <v>6198</v>
       </c>
     </row>
     <row r="4">
@@ -513,19 +528,19 @@
         <v>8</v>
       </c>
       <c r="B4" t="n">
-        <v>0.258959177313805</v>
+        <v>0.244900379506641</v>
       </c>
       <c r="C4" t="n">
-        <v>0.209474724654053</v>
+        <v>0.195919997542167</v>
       </c>
       <c r="D4" t="n">
-        <v>0.269872656806138</v>
+        <v>0.229883043497306</v>
       </c>
       <c r="E4" t="n">
-        <v>0.19933762649494</v>
+        <v>0.18817057232303</v>
       </c>
       <c r="F4" t="n">
-        <v>0.193542003364227</v>
+        <v>0.188469257434775</v>
       </c>
     </row>
     <row r="5">
@@ -533,19 +548,19 @@
         <v>9</v>
       </c>
       <c r="B5" t="n">
-        <v>619</v>
+        <v>507</v>
       </c>
       <c r="C5" t="n">
-        <v>229</v>
+        <v>123</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>531</v>
+        <v>170</v>
       </c>
       <c r="F5" t="n">
-        <v>1004</v>
+        <v>142</v>
       </c>
     </row>
     <row r="6">
@@ -553,19 +568,19 @@
         <v>10</v>
       </c>
       <c r="B6" t="n">
-        <v>0.560566637756577</v>
+        <v>0.596993350679387</v>
       </c>
       <c r="C6" t="n">
-        <v>0.571841572708875</v>
+        <v>0.614532138382962</v>
       </c>
       <c r="D6" t="n">
-        <v>0.328804085959333</v>
+        <v>0.505733834441553</v>
       </c>
       <c r="E6" t="n">
-        <v>0.522019851594873</v>
+        <v>0.59660788281777</v>
       </c>
       <c r="F6" t="n">
-        <v>0.565481352992194</v>
+        <v>0.5972824515756</v>
       </c>
     </row>
     <row r="7">
@@ -573,19 +588,19 @@
         <v>11</v>
       </c>
       <c r="B7" t="n">
-        <v>221547</v>
+        <v>620540</v>
       </c>
       <c r="C7" t="n">
-        <v>208131</v>
+        <v>581031</v>
       </c>
       <c r="D7" t="n">
-        <v>21948</v>
+        <v>58470</v>
       </c>
       <c r="E7" t="n">
-        <v>46911</v>
+        <v>132363</v>
       </c>
       <c r="F7" t="n">
-        <v>256074</v>
+        <v>724157</v>
       </c>
     </row>
     <row r="8">
@@ -593,19 +608,19 @@
         <v>12</v>
       </c>
       <c r="B8" t="n">
-        <v>0.0001986035</v>
+        <v>0.000141812</v>
       </c>
       <c r="C8" t="n">
-        <v>0.00021621</v>
+        <v>0.0001548971</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0002278112</v>
+        <v>0.0001539251</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0002344866</v>
+        <v>0.0001813196</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0001835407</v>
+        <v>0.0001325679</v>
       </c>
     </row>
     <row r="9">
@@ -613,87 +628,97 @@
         <v>13</v>
       </c>
       <c r="B9" t="n">
-        <v>0.10638298</v>
+        <v>0.01275222</v>
       </c>
       <c r="C9" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="D9"/>
+        <v>0.012699906</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.001714939</v>
+      </c>
       <c r="E9" t="n">
-        <v>0.02941176</v>
+        <v>0.003875969</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1969697</v>
+        <v>0.013711889</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
         <v>14</v>
       </c>
-      <c r="B10" t="e">
-        <v>#NUM!</v>
-      </c>
-      <c r="C10" t="e">
-        <v>#NUM!</v>
-      </c>
-      <c r="D10" t="e">
-        <v>#NUM!</v>
-      </c>
-      <c r="E10" t="e">
-        <v>#NUM!</v>
-      </c>
-      <c r="F10" t="e">
-        <v>#NUM!</v>
+      <c r="B10" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.5833333</v>
+      </c>
+      <c r="D10"/>
+      <c r="E10" t="n">
+        <v>0.1666667</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2.0909091</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
         <v>15</v>
       </c>
-      <c r="B11" t="e">
-        <v>#NUM!</v>
-      </c>
-      <c r="C11" t="e">
-        <v>#NUM!</v>
-      </c>
-      <c r="D11" t="e">
-        <v>#NUM!</v>
-      </c>
-      <c r="E11" t="e">
-        <v>#NUM!</v>
-      </c>
-      <c r="F11" t="e">
-        <v>#NUM!</v>
+      <c r="B11" t="n">
+        <v>0.0000016115</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.000003442157</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.00003420558</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.00001510996</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
         <v>16</v>
       </c>
-      <c r="B12"/>
-      <c r="C12"/>
-      <c r="D12"/>
-      <c r="E12"/>
-      <c r="F12"/>
+      <c r="B12" t="n">
+        <v>0.0001614205</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.0003135779</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.0003810976</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.0003229974</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
         <v>17</v>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0.000284821032514858</v>
+        <v>0</v>
+      </c>
+      <c r="D13" t="e">
+        <v>#NUM!</v>
       </c>
       <c r="E13" t="n">
-        <v>1</v>
+        <v>0.1666667</v>
       </c>
       <c r="F13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -701,19 +726,19 @@
         <v>18</v>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>62.4632367753112</v>
       </c>
       <c r="C14" t="n">
-        <v>0.876889841702408</v>
+        <v>65.4543076266402</v>
       </c>
       <c r="D14" t="n">
-        <v>0.944923365791498</v>
+        <v>73.4256883872071</v>
       </c>
       <c r="E14" t="n">
-        <v>0.799899982914148</v>
+        <v>71.7775144791244</v>
       </c>
       <c r="F14" t="n">
-        <v>0.985254451347966</v>
+        <v>59.3544561244203</v>
       </c>
     </row>
     <row r="15">
@@ -721,19 +746,19 @@
         <v>19</v>
       </c>
       <c r="B15" t="n">
-        <v>1</v>
+        <v>1.66405495331115</v>
       </c>
       <c r="C15" t="n">
-        <v>1</v>
+        <v>1.89471691344985</v>
       </c>
       <c r="D15" t="n">
-        <v>1</v>
+        <v>2.76303256532372</v>
       </c>
       <c r="E15" t="n">
-        <v>1</v>
+        <v>2.54327402971053</v>
       </c>
       <c r="F15" t="n">
-        <v>1</v>
+        <v>1.46029430203002</v>
       </c>
     </row>
     <row r="16">
@@ -741,19 +766,19 @@
         <v>20</v>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -761,19 +786,19 @@
         <v>21</v>
       </c>
       <c r="B17" t="n">
-        <v>0.127638219523925</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0.718696580572807</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0.535003825022633</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>0.804005680081437</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>0.596692408540112</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -781,19 +806,19 @@
         <v>22</v>
       </c>
       <c r="B18" t="n">
-        <v>0.0000000208325080548998</v>
+        <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>0.0000937802472700193</v>
+        <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.000592525885325618</v>
+        <v>0.0000751876024143293</v>
       </c>
       <c r="E18" t="n">
-        <v>0.000116019857998753</v>
+        <v>1</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0000196574687618419</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -801,19 +826,19 @@
         <v>23</v>
       </c>
       <c r="B19" t="n">
-        <v>0.000000465814115693489</v>
+        <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>0.000000575811768284216</v>
+        <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.00000437263661244611</v>
+        <v>1</v>
       </c>
       <c r="E19" t="n">
-        <v>0.00000298253686307848</v>
+        <v>1</v>
       </c>
       <c r="F19" t="n">
-        <v>0.00000154964560269668</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -821,19 +846,19 @@
         <v>24</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>0.976127451382265</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>0.910958886038645</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -861,19 +886,19 @@
         <v>26</v>
       </c>
       <c r="B22" t="n">
-        <v>1</v>
+        <v>0.000000000252440964436926</v>
       </c>
       <c r="C22" t="n">
-        <v>1</v>
+        <v>0.00000367406994987658</v>
       </c>
       <c r="D22" t="n">
-        <v>1</v>
+        <v>0.0000751876024143293</v>
       </c>
       <c r="E22" t="n">
-        <v>1</v>
+        <v>0.0000110777383562982</v>
       </c>
       <c r="F22" t="n">
-        <v>1</v>
+        <v>0.00000198914494101647</v>
       </c>
     </row>
     <row r="23">
@@ -881,19 +906,19 @@
         <v>27</v>
       </c>
       <c r="B23" t="n">
-        <v>0</v>
+        <v>0.228406610375343</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>0.948574470895323</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>0.709999092724087</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>0.996922391524355</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>0.814280508871197</v>
       </c>
     </row>
     <row r="24">
@@ -901,19 +926,19 @@
         <v>28</v>
       </c>
       <c r="B24" t="n">
-        <v>-0.374510351893461</v>
+        <v>0.0000035404396916874</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.383332679440919</v>
+        <v>0.00000367406994987658</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.348924004491255</v>
+        <v>0.0000224623361145156</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.374416539687446</v>
+        <v>0.0000121531470159856</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.291102839517211</v>
+        <v>0.00000540810800237351</v>
       </c>
     </row>
     <row r="25">
@@ -933,7 +958,7 @@
         <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>3.47552709729671e-309</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -941,19 +966,19 @@
         <v>30</v>
       </c>
       <c r="B26" t="n">
-        <v>24652</v>
+        <v>1</v>
       </c>
       <c r="C26" t="n">
-        <v>31531</v>
+        <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>18251</v>
+        <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>32288</v>
+        <v>1</v>
       </c>
       <c r="F26" t="n">
-        <v>32363</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -961,19 +986,19 @@
         <v>31</v>
       </c>
       <c r="B27" t="n">
-        <v>0.00000000000101608607386667</v>
+        <v>1</v>
       </c>
       <c r="C27" t="n">
-        <v>0.00000000000000000000000000095650904151226</v>
+        <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>0.00000000000000000000000000000000000000000000000000000000000000000000024526843932002</v>
+        <v>1</v>
       </c>
       <c r="E27" t="n">
-        <v>0.000000127249144713242</v>
+        <v>1</v>
       </c>
       <c r="F27" t="n">
-        <v>0.00000303968704385543</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -981,19 +1006,19 @@
         <v>32</v>
       </c>
       <c r="B28" t="n">
-        <v>0.188986025158784</v>
+        <v>0</v>
       </c>
       <c r="C28" t="n">
-        <v>0.161515494763564</v>
+        <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>0.135093699669746</v>
+        <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>0.210756049015721</v>
+        <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>0.131639190489797</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -1001,19 +1026,19 @@
         <v>33</v>
       </c>
       <c r="B29" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000178510514560944</v>
+        <v>-0.521156154807479</v>
       </c>
       <c r="C29" t="n">
-        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000503006457200903</v>
+        <v>-0.534794048032166</v>
       </c>
       <c r="D29" t="n">
-        <v>0.0000000000000000000000000000000000000000000000000000449314401017162</v>
+        <v>-0.50050597786933</v>
       </c>
       <c r="E29" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000599621093929318</v>
+        <v>-0.532027868812699</v>
       </c>
       <c r="F29" t="n">
-        <v>0.0000000000000000000000000000000000000000000000000000000000000354015550787252</v>
+        <v>-0.427515425131733</v>
       </c>
     </row>
     <row r="30">
@@ -1021,19 +1046,19 @@
         <v>34</v>
       </c>
       <c r="B30" t="n">
-        <v>-0.0774577419515716</v>
+        <v>0</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.0607706927847583</v>
+        <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.00562573497474704</v>
+        <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.0451891863000795</v>
+        <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.0570168913521124</v>
+        <v>3.28958140295421e-273</v>
       </c>
     </row>
     <row r="31">
@@ -1041,19 +1066,119 @@
         <v>35</v>
       </c>
       <c r="B31" t="n">
-        <v>0.000000000000000000000364306052412232</v>
+        <v>24652</v>
       </c>
       <c r="C31" t="n">
-        <v>0.0000000000000151352963413635</v>
+        <v>31531</v>
       </c>
       <c r="D31" t="n">
-        <v>0.784618415544612</v>
+        <v>18251</v>
       </c>
       <c r="E31" t="n">
-        <v>0.0000000307818730430294</v>
+        <v>32288</v>
       </c>
       <c r="F31" t="n">
-        <v>0.00000000000160517997433082</v>
+        <v>32363</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s">
+        <v>36</v>
+      </c>
+      <c r="B32" t="n">
+        <v>0.00000000000101608607386667</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.00000000000000000000000000095650904151226</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0.00000000000000000000000000000000000000000000000000000000000000000000024526843932002</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.000000127249144713242</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.00000303968704385543</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s">
+        <v>37</v>
+      </c>
+      <c r="B33" t="n">
+        <v>0.188654870721136</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.161861633975117</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0.134987191025296</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.209934247364943</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.131539275392021</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s">
+        <v>38</v>
+      </c>
+      <c r="B34" t="n">
+        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000169113887760563</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000865903352104235</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0.0000000000000000000000000000000000000000000000000000358450988924406</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000331276603508069</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0.0000000000000000000000000000000000000000000000000000000000000280731906029148</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s">
+        <v>39</v>
+      </c>
+      <c r="B35" t="n">
+        <v>-0.0780049990662349</v>
+      </c>
+      <c r="C35" t="n">
+        <v>-0.061154944654926</v>
+      </c>
+      <c r="D35" t="n">
+        <v>-0.0057013036303191</v>
+      </c>
+      <c r="E35" t="n">
+        <v>-0.0450628442785801</v>
+      </c>
+      <c r="F35" t="n">
+        <v>-0.0567609646289818</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s">
+        <v>40</v>
+      </c>
+      <c r="B36" t="n">
+        <v>0.000000000000000000000152043898348793</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.00000000000000909677854312602</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0.775172880394222</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.0000000320018846373988</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.00000000000187262453484095</v>
       </c>
     </row>
   </sheetData>

--- a/Dataset_2/4_Integration_results/Stats_table_final.xlsx
+++ b/Dataset_2/4_Integration_results/Stats_table_final.xlsx
@@ -672,10 +672,10 @@
         <v>0.000003442157</v>
       </c>
       <c r="D11" t="n">
-        <v>0.00003420558</v>
+        <v>0.000034205576</v>
       </c>
       <c r="E11" t="n">
-        <v>0.00001510996</v>
+        <v>0.000015109963</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>

--- a/Dataset_2/4_Integration_results/Stats_table_final.xlsx
+++ b/Dataset_2/4_Integration_results/Stats_table_final.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
   <si>
     <t xml:space="preserve">metric</t>
   </si>
@@ -99,18 +99,6 @@
   </si>
   <si>
     <t xml:space="preserve">DM ∩ DE vs All DM down (padj)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hypo-up (padj)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hypo-down (padj)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hyper-up (padj)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hyper-down (padj)</t>
   </si>
   <si>
     <t xml:space="preserve">meth Spear (rho)</t>
@@ -508,19 +496,19 @@
         <v>7</v>
       </c>
       <c r="B3" t="n">
-        <v>6195</v>
+        <v>6482</v>
       </c>
       <c r="C3" t="n">
-        <v>6377</v>
+        <v>6675</v>
       </c>
       <c r="D3" t="n">
-        <v>5248</v>
+        <v>5435</v>
       </c>
       <c r="E3" t="n">
-        <v>6191</v>
+        <v>6480</v>
       </c>
       <c r="F3" t="n">
-        <v>6198</v>
+        <v>6487</v>
       </c>
     </row>
     <row r="4">
@@ -528,19 +516,19 @@
         <v>8</v>
       </c>
       <c r="B4" t="n">
-        <v>0.244900379506641</v>
+        <v>0.256246046805819</v>
       </c>
       <c r="C4" t="n">
-        <v>0.195919997542167</v>
+        <v>0.205075424744232</v>
       </c>
       <c r="D4" t="n">
-        <v>0.229883043497306</v>
+        <v>0.238074379079241</v>
       </c>
       <c r="E4" t="n">
-        <v>0.18817057232303</v>
+        <v>0.196954499863226</v>
       </c>
       <c r="F4" t="n">
-        <v>0.188469257434775</v>
+        <v>0.197257191510065</v>
       </c>
     </row>
     <row r="5">
@@ -568,19 +556,19 @@
         <v>10</v>
       </c>
       <c r="B6" t="n">
-        <v>0.596993350679387</v>
+        <v>0.581971628658646</v>
       </c>
       <c r="C6" t="n">
-        <v>0.614532138382962</v>
+        <v>0.599299694738732</v>
       </c>
       <c r="D6" t="n">
-        <v>0.505733834441553</v>
+        <v>0.487969114742324</v>
       </c>
       <c r="E6" t="n">
-        <v>0.59660788281777</v>
+        <v>0.581792063207039</v>
       </c>
       <c r="F6" t="n">
-        <v>0.5972824515756</v>
+        <v>0.582420542287664</v>
       </c>
     </row>
     <row r="7">
@@ -588,19 +576,19 @@
         <v>11</v>
       </c>
       <c r="B7" t="n">
-        <v>620540</v>
+        <v>634783</v>
       </c>
       <c r="C7" t="n">
-        <v>581031</v>
+        <v>590804</v>
       </c>
       <c r="D7" t="n">
-        <v>58470</v>
+        <v>59553</v>
       </c>
       <c r="E7" t="n">
-        <v>132363</v>
+        <v>137029</v>
       </c>
       <c r="F7" t="n">
-        <v>724157</v>
+        <v>747757</v>
       </c>
     </row>
     <row r="8">
@@ -608,19 +596,19 @@
         <v>12</v>
       </c>
       <c r="B8" t="n">
-        <v>0.000141812</v>
+        <v>0.0001402054</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0001548971</v>
+        <v>0.0001540274</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0001539251</v>
+        <v>0.0001511259</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0001813196</v>
+        <v>0.0001751454</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0001325679</v>
+        <v>0.000132396</v>
       </c>
     </row>
     <row r="9">
@@ -628,19 +616,19 @@
         <v>13</v>
       </c>
       <c r="B9" t="n">
-        <v>0.01275222</v>
+        <v>0.01234187</v>
       </c>
       <c r="C9" t="n">
-        <v>0.012699906</v>
+        <v>0.012282804</v>
       </c>
       <c r="D9" t="n">
-        <v>0.001714939</v>
+        <v>0.001655934</v>
       </c>
       <c r="E9" t="n">
-        <v>0.003875969</v>
+        <v>0.003703132</v>
       </c>
       <c r="F9" t="n">
-        <v>0.013711889</v>
+        <v>0.013563502</v>
       </c>
     </row>
     <row r="10">
@@ -651,14 +639,14 @@
         <v>0.45</v>
       </c>
       <c r="C10" t="n">
-        <v>0.5833333</v>
+        <v>0.5</v>
       </c>
       <c r="D10"/>
       <c r="E10" t="n">
         <v>0.1666667</v>
       </c>
       <c r="F10" t="n">
-        <v>2.0909091</v>
+        <v>1.8461538</v>
       </c>
     </row>
     <row r="11">
@@ -666,16 +654,16 @@
         <v>15</v>
       </c>
       <c r="B11" t="n">
-        <v>0.0000016115</v>
+        <v>0.000001575341</v>
       </c>
       <c r="C11" t="n">
-        <v>0.000003442157</v>
+        <v>0.000003385217</v>
       </c>
       <c r="D11" t="n">
-        <v>0.000034205576</v>
+        <v>0.00003358353</v>
       </c>
       <c r="E11" t="n">
-        <v>0.000015109963</v>
+        <v>0.0000583818</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -686,16 +674,16 @@
         <v>16</v>
       </c>
       <c r="B12" t="n">
-        <v>0.0001614205</v>
+        <v>0.0001542734</v>
       </c>
       <c r="C12" t="n">
-        <v>0.0003135779</v>
+        <v>0.0002995806</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0003810976</v>
+        <v>0.0003679853</v>
       </c>
       <c r="E12" t="n">
-        <v>0.0003229974</v>
+        <v>0.0012343774</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -711,11 +699,9 @@
       <c r="C13" t="n">
         <v>0</v>
       </c>
-      <c r="D13" t="e">
-        <v>#NUM!</v>
-      </c>
+      <c r="D13"/>
       <c r="E13" t="n">
-        <v>0.1666667</v>
+        <v>1</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -726,19 +712,19 @@
         <v>18</v>
       </c>
       <c r="B14" t="n">
-        <v>62.4632367753112</v>
+        <v>62.4560469336829</v>
       </c>
       <c r="C14" t="n">
-        <v>65.4543076266402</v>
+        <v>65.3586982831434</v>
       </c>
       <c r="D14" t="n">
-        <v>73.4256883872071</v>
+        <v>73.1331754907393</v>
       </c>
       <c r="E14" t="n">
-        <v>71.7775144791244</v>
+        <v>71.3287610796936</v>
       </c>
       <c r="F14" t="n">
-        <v>59.3544561244203</v>
+        <v>59.2871920509731</v>
       </c>
     </row>
     <row r="15">
@@ -746,19 +732,19 @@
         <v>19</v>
       </c>
       <c r="B15" t="n">
-        <v>1.66405495331115</v>
+        <v>1.66354477439713</v>
       </c>
       <c r="C15" t="n">
-        <v>1.89471691344985</v>
+        <v>1.88672754902104</v>
       </c>
       <c r="D15" t="n">
-        <v>2.76303256532372</v>
+        <v>2.7220625</v>
       </c>
       <c r="E15" t="n">
-        <v>2.54327402971053</v>
+        <v>2.48781579609994</v>
       </c>
       <c r="F15" t="n">
-        <v>1.46029430203002</v>
+        <v>1.45622950215573</v>
       </c>
     </row>
     <row r="16">
@@ -806,19 +792,19 @@
         <v>22</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>0.999999999998798</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>0.999999999999997</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0000751876024143293</v>
+        <v>0.999996587506708</v>
       </c>
       <c r="E18" t="n">
         <v>1</v>
       </c>
       <c r="F18" t="n">
-        <v>1</v>
+        <v>0.999999999999969</v>
       </c>
     </row>
     <row r="19">
@@ -826,19 +812,19 @@
         <v>23</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>0.999999999998798</v>
       </c>
       <c r="C19" t="n">
-        <v>1</v>
+        <v>0.999999999999997</v>
       </c>
       <c r="D19" t="n">
-        <v>1</v>
+        <v>0.999996587506708</v>
       </c>
       <c r="E19" t="n">
         <v>1</v>
       </c>
       <c r="F19" t="n">
-        <v>1</v>
+        <v>0.999999999999969</v>
       </c>
     </row>
     <row r="20">
@@ -846,19 +832,19 @@
         <v>24</v>
       </c>
       <c r="B20" t="n">
+        <v>0.999999999998798</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.999999999999997</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.999996587506708</v>
+      </c>
+      <c r="E20" t="n">
         <v>1</v>
       </c>
-      <c r="C20" t="n">
-        <v>0.976127451382265</v>
-      </c>
-      <c r="D20" t="n">
-        <v>1</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0.910958886038645</v>
-      </c>
       <c r="F20" t="n">
-        <v>1</v>
+        <v>0.999999999999969</v>
       </c>
     </row>
     <row r="21">
@@ -866,19 +852,19 @@
         <v>25</v>
       </c>
       <c r="B21" t="n">
-        <v>1</v>
+        <v>0.999999999998798</v>
       </c>
       <c r="C21" t="n">
-        <v>1</v>
+        <v>0.999999999999997</v>
       </c>
       <c r="D21" t="n">
-        <v>1</v>
+        <v>0.999996587506708</v>
       </c>
       <c r="E21" t="n">
         <v>1</v>
       </c>
       <c r="F21" t="n">
-        <v>1</v>
+        <v>0.999999999999969</v>
       </c>
     </row>
     <row r="22">
@@ -886,19 +872,19 @@
         <v>26</v>
       </c>
       <c r="B22" t="n">
-        <v>0.000000000252440964436926</v>
+        <v>0.000000000259172723488577</v>
       </c>
       <c r="C22" t="n">
-        <v>0.00000367406994987658</v>
+        <v>0.00000428368872347555</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0000751876024143293</v>
+        <v>0.0000882201201661464</v>
       </c>
       <c r="E22" t="n">
-        <v>0.0000110777383562982</v>
+        <v>0.0000113731447124661</v>
       </c>
       <c r="F22" t="n">
-        <v>0.00000198914494101647</v>
+        <v>0.00000218805943511811</v>
       </c>
     </row>
     <row r="23">
@@ -906,19 +892,19 @@
         <v>27</v>
       </c>
       <c r="B23" t="n">
-        <v>0.228406610375343</v>
+        <v>0.0940672573854915</v>
       </c>
       <c r="C23" t="n">
-        <v>0.948574470895323</v>
+        <v>0.479808896226916</v>
       </c>
       <c r="D23" t="n">
-        <v>0.709999092724087</v>
+        <v>0.338808061685223</v>
       </c>
       <c r="E23" t="n">
-        <v>0.996922391524355</v>
+        <v>0.677624390857269</v>
       </c>
       <c r="F23" t="n">
-        <v>0.814280508871197</v>
+        <v>0.466560592906334</v>
       </c>
     </row>
     <row r="24">
@@ -926,19 +912,19 @@
         <v>28</v>
       </c>
       <c r="B24" t="n">
-        <v>0.0000035404396916874</v>
+        <v>0.0000521912105691731</v>
       </c>
       <c r="C24" t="n">
-        <v>0.00000367406994987658</v>
+        <v>0.0000267884937702907</v>
       </c>
       <c r="D24" t="n">
-        <v>0.0000224623361145156</v>
+        <v>0.0000827745469123982</v>
       </c>
       <c r="E24" t="n">
-        <v>0.0000121531470159856</v>
+        <v>0.0000980290280340864</v>
       </c>
       <c r="F24" t="n">
-        <v>0.00000540810800237351</v>
+        <v>0.0000650201597434813</v>
       </c>
     </row>
     <row r="25">
@@ -946,19 +932,19 @@
         <v>29</v>
       </c>
       <c r="B25" t="n">
-        <v>0</v>
+        <v>-0.51506173045605</v>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>-0.526541913097766</v>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>-0.493699275367445</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>-0.524970599518909</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>-0.422572619383573</v>
       </c>
     </row>
     <row r="26">
@@ -966,19 +952,19 @@
         <v>30</v>
       </c>
       <c r="B26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>1</v>
+        <v>2.57202589954231e-278</v>
       </c>
     </row>
     <row r="27">
@@ -986,19 +972,19 @@
         <v>31</v>
       </c>
       <c r="B27" t="n">
-        <v>1</v>
+        <v>24652</v>
       </c>
       <c r="C27" t="n">
-        <v>1</v>
+        <v>31531</v>
       </c>
       <c r="D27" t="n">
-        <v>1</v>
+        <v>18251</v>
       </c>
       <c r="E27" t="n">
-        <v>1</v>
+        <v>32288</v>
       </c>
       <c r="F27" t="n">
-        <v>1</v>
+        <v>32363</v>
       </c>
     </row>
     <row r="28">
@@ -1006,19 +992,19 @@
         <v>32</v>
       </c>
       <c r="B28" t="n">
-        <v>0</v>
+        <v>0.000000000000536140523261102</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>0.0000000000000000000000000159325710429417</v>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>0.000000000000000000000000000000000000000000000000000000000000000000113451633628902</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>0.000000106984100930472</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>0.00000349563919957613</v>
       </c>
     </row>
     <row r="29">
@@ -1026,19 +1012,19 @@
         <v>33</v>
       </c>
       <c r="B29" t="n">
-        <v>-0.521156154807479</v>
+        <v>0.188654870721136</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.534794048032166</v>
+        <v>0.161861633975117</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.50050597786933</v>
+        <v>0.134987191025296</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.532027868812699</v>
+        <v>0.209934247364943</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.427515425131733</v>
+        <v>0.131539275392021</v>
       </c>
     </row>
     <row r="30">
@@ -1046,19 +1032,19 @@
         <v>34</v>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000248033702048826</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000126999158308621</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>0.000000000000000000000000000000000000000000000000000043810676424094</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000485872351811835</v>
       </c>
       <c r="F30" t="n">
-        <v>3.28958140295421e-273</v>
+        <v>0.0000000000000000000000000000000000000000000000000000000000000411740128842751</v>
       </c>
     </row>
     <row r="31">
@@ -1066,19 +1052,19 @@
         <v>35</v>
       </c>
       <c r="B31" t="n">
-        <v>24652</v>
+        <v>-0.0780049990662349</v>
       </c>
       <c r="C31" t="n">
-        <v>31531</v>
+        <v>-0.061154944654926</v>
       </c>
       <c r="D31" t="n">
-        <v>18251</v>
+        <v>-0.0057013036303191</v>
       </c>
       <c r="E31" t="n">
-        <v>32288</v>
+        <v>-0.0450628442785801</v>
       </c>
       <c r="F31" t="n">
-        <v>32363</v>
+        <v>-0.0567609646289818</v>
       </c>
     </row>
     <row r="32">
@@ -1086,99 +1072,19 @@
         <v>36</v>
       </c>
       <c r="B32" t="n">
-        <v>0.00000000000101608607386667</v>
+        <v>0.000000000000000000000185831431315191</v>
       </c>
       <c r="C32" t="n">
-        <v>0.00000000000000000000000000095650904151226</v>
+        <v>0.0000000000000100064563974386</v>
       </c>
       <c r="D32" t="n">
-        <v>0.00000000000000000000000000000000000000000000000000000000000000000000024526843932002</v>
+        <v>0.812085874698708</v>
       </c>
       <c r="E32" t="n">
-        <v>0.000000127249144713242</v>
+        <v>0.0000000391134145568207</v>
       </c>
       <c r="F32" t="n">
-        <v>0.00000303968704385543</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="s">
-        <v>37</v>
-      </c>
-      <c r="B33" t="n">
-        <v>0.188654870721136</v>
-      </c>
-      <c r="C33" t="n">
-        <v>0.161861633975117</v>
-      </c>
-      <c r="D33" t="n">
-        <v>0.134987191025296</v>
-      </c>
-      <c r="E33" t="n">
-        <v>0.209934247364943</v>
-      </c>
-      <c r="F33" t="n">
-        <v>0.131539275392021</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="s">
-        <v>38</v>
-      </c>
-      <c r="B34" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000169113887760563</v>
-      </c>
-      <c r="C34" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000865903352104235</v>
-      </c>
-      <c r="D34" t="n">
-        <v>0.0000000000000000000000000000000000000000000000000000358450988924406</v>
-      </c>
-      <c r="E34" t="n">
-        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000331276603508069</v>
-      </c>
-      <c r="F34" t="n">
-        <v>0.0000000000000000000000000000000000000000000000000000000000000280731906029148</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="s">
-        <v>39</v>
-      </c>
-      <c r="B35" t="n">
-        <v>-0.0780049990662349</v>
-      </c>
-      <c r="C35" t="n">
-        <v>-0.061154944654926</v>
-      </c>
-      <c r="D35" t="n">
-        <v>-0.0057013036303191</v>
-      </c>
-      <c r="E35" t="n">
-        <v>-0.0450628442785801</v>
-      </c>
-      <c r="F35" t="n">
-        <v>-0.0567609646289818</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="s">
-        <v>40</v>
-      </c>
-      <c r="B36" t="n">
-        <v>0.000000000000000000000152043898348793</v>
-      </c>
-      <c r="C36" t="n">
-        <v>0.00000000000000909677854312602</v>
-      </c>
-      <c r="D36" t="n">
-        <v>0.775172880394222</v>
-      </c>
-      <c r="E36" t="n">
-        <v>0.0000000320018846373988</v>
-      </c>
-      <c r="F36" t="n">
-        <v>0.00000000000187262453484095</v>
+        <v>0.00000000000228876332036116</v>
       </c>
     </row>
   </sheetData>
